--- a/data/sample_era.xlsx
+++ b/data/sample_era.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46069.375</v>
+        <v>46070.375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46157.375</v>
+        <v>46158.375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46159.375</v>
+        <v>46160.375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46174.375</v>
+        <v>46175.375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46249.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46069.375</v>
+        <v>46070.375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46159.375</v>
+        <v>46160.375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46174.375</v>
+        <v>46175.375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46249.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46069.375</v>
+        <v>46070.375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>46159.375</v>
+        <v>46160.375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46174.375</v>
+        <v>46175.375</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46249.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46069.375</v>
+        <v>46070.375</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46219.375</v>
+        <v>46220.375</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46249.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46069.375</v>
+        <v>46070.375</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46249.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46069.375</v>
+        <v>46070.375</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46249.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>46069.375</v>
+        <v>46070.375</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46159.375</v>
+        <v>46160.375</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>46174.375</v>
+        <v>46175.375</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>46249.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>46069.375</v>
+        <v>46070.375</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>46249.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46069.375</v>
+        <v>46070.375</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46159.375</v>
+        <v>46160.375</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46174.375</v>
+        <v>46175.375</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46249.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>45909.375</v>
+        <v>45910.375</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>45914.375</v>
+        <v>45915.375</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>46069.375</v>
+        <v>46070.375</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>46249.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>46069.375</v>
+        <v>46070.375</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>46249.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>46069.375</v>
+        <v>46070.375</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>46249.375</v>
+        <v>46250.375</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2047,6 +2047,76 @@
         </is>
       </c>
       <c r="G43" t="inlineStr">
+        <is>
+          <t>Замечаний нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>46070.375</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Работа</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Спуск оборудования</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ввод после ремонта</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>УЭЦН-5-80, НКТ-73 с покрытием</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Оборудование спущено</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>46250.375</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Работа</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Плановая диагностика</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>График диагностики</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>УЭЦН-5-80, НКТ-73 с покрытием</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>Замечаний нет</t>
         </is>
